--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -68,6 +82,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -83,6 +104,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1109,6 +1137,17 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"捷克克朗,波兰兹罗提,英镑,欧元,泰铢,巴西雷亚尔,墨西哥比索,印度卢比,肯尼亚先令,韩元,澳门元,港币,印尼盾,菲律宾比索,日元,加拿大元,新加坡元,人民币,美元,澳大利亚元,瑞典克朗,林吉特,新台币元,阿联酋迪拉姆,丹麦克朗,俄罗斯卢布,南非兰特,挪威克朗,瑞士法郎,沙特里亚尔,新土耳其里拉,新西兰元,匈牙利福林,以色列谢克尔,越南盾"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
+      <formula1>"保修,过期,破损,质量问题,滞销,其他,描述不符,下单错误"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <rPr>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>单据类型</t>
+  </si>
+  <si>
+    <t>退货物流单号</t>
   </si>
   <si>
     <r>
@@ -763,8 +766,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1081,28 +1087,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="11.75" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="13.375" customWidth="1"/>
-    <col min="12" max="12" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="13" max="13" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1114,10 +1121,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1135,16 +1142,20 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>"捷克克朗,波兰兹罗提,英镑,欧元,泰铢,巴西雷亚尔,墨西哥比索,印度卢比,肯尼亚先令,韩元,澳门元,港币,印尼盾,菲律宾比索,日元,加拿大元,新加坡元,人民币,美元,澳大利亚元,瑞典克朗,林吉特,新台币元,阿联酋迪拉姆,丹麦克朗,俄罗斯卢布,南非兰特,挪威克朗,瑞士法郎,沙特里亚尔,新土耳其里拉,新西兰元,匈牙利福林,以色列谢克尔,越南盾"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
       <formula1>"保修,过期,破损,质量问题,滞销,其他,描述不符,下单错误"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
       <rPr>
@@ -72,6 +72,21 @@
         <scheme val="minor"/>
       </rPr>
       <t>退货仓库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>退货类型</t>
     </r>
   </si>
   <si>
@@ -1087,47 +1102,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="13.375" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="14" max="14" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1145,17 +1160,23 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+      <formula1>"退货退款,退货补货"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
       <formula1>"捷克克朗,波兰兹罗提,英镑,欧元,泰铢,巴西雷亚尔,墨西哥比索,印度卢比,肯尼亚先令,韩元,澳门元,港币,印尼盾,菲律宾比索,日元,加拿大元,新加坡元,人民币,美元,澳大利亚元,瑞典克朗,林吉特,新台币元,阿联酋迪拉姆,丹麦克朗,俄罗斯卢布,南非兰特,挪威克朗,瑞士法郎,沙特里亚尔,新土耳其里拉,新西兰元,匈牙利福林,以色列谢克尔,越南盾"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
       <formula1>"保修,过期,破损,质量问题,滞销,其他,描述不符,下单错误"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,6 +76,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1167,7 +1174,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
-      <formula1>"退货退款,退货补货"</formula1>
+      <formula1>"退货退款,退货补货,买家退货,服务商退件,认领"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -1114,7 +1114,7 @@
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.25" customWidth="1"/>
@@ -1137,7 +1137,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -106,6 +106,12 @@
     <t>退货物流单号</t>
   </si>
   <si>
+    <t>第三方单据编号</t>
+  </si>
+  <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -178,7 +184,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +198,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF172B4D"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -658,137 +670,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -796,6 +808,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,25 +1124,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="13.375" customWidth="1"/>
-    <col min="14" max="14" width="18.375" customWidth="1"/>
+    <col min="6" max="8" width="14.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
+    <col min="10" max="10" width="14.625" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" ht="15.75" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1146,16 +1161,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1169,6 +1184,12 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1179,11 +1200,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G2:G1048576 H2:H1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"捷克克朗,波兰兹罗提,英镑,欧元,泰铢,巴西雷亚尔,墨西哥比索,印度卢比,肯尼亚先令,韩元,澳门元,港币,印尼盾,菲律宾比索,日元,加拿大元,新加坡元,人民币,美元,澳大利亚元,瑞典克朗,林吉特,新台币元,阿联酋迪拉姆,丹麦克朗,俄罗斯卢布,南非兰特,挪威克朗,瑞士法郎,沙特里亚尔,新土耳其里拉,新西兰元,匈牙利福林,以色列谢克尔,越南盾"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>"保修,过期,破损,质量问题,滞销,其他,描述不符,下单错误"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockTemplate.xlsx
@@ -1193,14 +1193,20 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+  <dataValidations count="7">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F2:H1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
+      <formula1>"退货退款,退货补货,买家退货,服务商退件,认领,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
+      <formula1>"B2B订单,B2C订单,售后订单-补/换/赠"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576">
       <formula1>"退货退款,退货补货,买家退货,服务商退件,认领"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576">
       <formula1>"B2B订单,B2C订单,头程物流单,退货入库单"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G2:G1048576 H2:H1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"捷克克朗,波兰兹罗提,英镑,欧元,泰铢,巴西雷亚尔,墨西哥比索,印度卢比,肯尼亚先令,韩元,澳门元,港币,印尼盾,菲律宾比索,日元,加拿大元,新加坡元,人民币,美元,澳大利亚元,瑞典克朗,林吉特,新台币元,阿联酋迪拉姆,丹麦克朗,俄罗斯卢布,南非兰特,挪威克朗,瑞士法郎,沙特里亚尔,新土耳其里拉,新西兰元,匈牙利福林,以色列谢克尔,越南盾"</formula1>
     </dataValidation>
